--- a/output/yearly_total_coral_cover_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_30_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256231045158257</v>
+        <v>1.249368628705572</v>
       </c>
       <c r="C3" t="n">
-        <v>4.710962392030581</v>
+        <v>4.609459496888503</v>
       </c>
       <c r="D3" t="n">
-        <v>6.041061873554358</v>
+        <v>6.074941986827914</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00825531074319</v>
+        <v>11.93377011242199</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.379950654010104</v>
+        <v>1.362429431609629</v>
       </c>
       <c r="C4" t="n">
-        <v>5.342151330709644</v>
+        <v>5.093011461238112</v>
       </c>
       <c r="D4" t="n">
-        <v>6.297837740819941</v>
+        <v>6.459130576044458</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01993972553969</v>
+        <v>12.9145714688922</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.547239080854313</v>
+        <v>1.516044315992087</v>
       </c>
       <c r="C5" t="n">
-        <v>6.161556963892551</v>
+        <v>5.688695029372046</v>
       </c>
       <c r="D5" t="n">
-        <v>6.542036996392227</v>
+        <v>6.793234254444998</v>
       </c>
       <c r="E5" t="n">
-        <v>14.25083304113909</v>
+        <v>13.99797359980913</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739063946964288</v>
+        <v>1.684064967212631</v>
       </c>
       <c r="C6" t="n">
-        <v>7.118959440805031</v>
+        <v>6.409086976530148</v>
       </c>
       <c r="D6" t="n">
-        <v>6.851392896251145</v>
+        <v>7.27789831219461</v>
       </c>
       <c r="E6" t="n">
-        <v>15.70941628402046</v>
+        <v>15.37105025593739</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.952581337586557</v>
+        <v>1.876735575466098</v>
       </c>
       <c r="C7" t="n">
-        <v>8.217685197250651</v>
+        <v>7.279311916748161</v>
       </c>
       <c r="D7" t="n">
-        <v>7.177106849659198</v>
+        <v>7.695149688141329</v>
       </c>
       <c r="E7" t="n">
-        <v>17.34737338449641</v>
+        <v>16.85119718035559</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.165668998376069</v>
+        <v>1.10873882453369</v>
       </c>
       <c r="C8" t="n">
-        <v>5.717578597163322</v>
+        <v>4.96606117075776</v>
       </c>
       <c r="D8" t="n">
-        <v>5.362746944388147</v>
+        <v>5.945571175853806</v>
       </c>
       <c r="E8" t="n">
-        <v>12.24599453992754</v>
+        <v>12.02037117114526</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.443963709760813</v>
+        <v>1.369934660081059</v>
       </c>
       <c r="C9" t="n">
-        <v>7.017851245987941</v>
+        <v>6.10816679582269</v>
       </c>
       <c r="D9" t="n">
-        <v>5.820116531067884</v>
+        <v>6.613852403009761</v>
       </c>
       <c r="E9" t="n">
-        <v>14.28193148681664</v>
+        <v>14.09195385891351</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.741359992013907</v>
+        <v>1.656393474781513</v>
       </c>
       <c r="C10" t="n">
-        <v>8.447126570751843</v>
+        <v>7.434116003821517</v>
       </c>
       <c r="D10" t="n">
-        <v>6.239358010729043</v>
+        <v>7.171321933479799</v>
       </c>
       <c r="E10" t="n">
-        <v>16.42784457349479</v>
+        <v>16.26183141208283</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.045960529118136</v>
+        <v>1.941532249639653</v>
       </c>
       <c r="C11" t="n">
-        <v>10.01451769038339</v>
+        <v>8.846662815665066</v>
       </c>
       <c r="D11" t="n">
-        <v>6.662324766550444</v>
+        <v>7.733531816960991</v>
       </c>
       <c r="E11" t="n">
-        <v>18.72280298605197</v>
+        <v>18.52172688226571</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.347073211324902</v>
+        <v>2.231235535447297</v>
       </c>
       <c r="C12" t="n">
-        <v>11.68580069095421</v>
+        <v>10.39789816479631</v>
       </c>
       <c r="D12" t="n">
-        <v>7.068502755544201</v>
+        <v>8.391370513008722</v>
       </c>
       <c r="E12" t="n">
-        <v>21.10137665782331</v>
+        <v>21.02050421325233</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.634708923005391</v>
+        <v>2.509484319887061</v>
       </c>
       <c r="C13" t="n">
-        <v>13.44506817534501</v>
+        <v>11.9484673495148</v>
       </c>
       <c r="D13" t="n">
-        <v>7.524794844507571</v>
+        <v>8.937738707451915</v>
       </c>
       <c r="E13" t="n">
-        <v>23.60457194285797</v>
+        <v>23.39569037685377</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.522386347498486</v>
+        <v>1.448038593855876</v>
       </c>
       <c r="C14" t="n">
-        <v>9.53933810037794</v>
+        <v>8.360357282347945</v>
       </c>
       <c r="D14" t="n">
-        <v>5.726220199606285</v>
+        <v>6.759656920481691</v>
       </c>
       <c r="E14" t="n">
-        <v>16.78794464748271</v>
+        <v>16.56805279668551</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.543238668736689</v>
+        <v>1.471178387244973</v>
       </c>
       <c r="C15" t="n">
-        <v>10.33291422215176</v>
+        <v>9.049819060086396</v>
       </c>
       <c r="D15" t="n">
-        <v>5.695481678986319</v>
+        <v>6.834475913022341</v>
       </c>
       <c r="E15" t="n">
-        <v>17.57163456987477</v>
+        <v>17.35547336035371</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.769148632960923</v>
+        <v>1.696460032938488</v>
       </c>
       <c r="C16" t="n">
-        <v>12.28793714795773</v>
+        <v>10.7194675632219</v>
       </c>
       <c r="D16" t="n">
-        <v>6.076645225160142</v>
+        <v>7.394297906415</v>
       </c>
       <c r="E16" t="n">
-        <v>20.1337310060788</v>
+        <v>19.81022550257539</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.404517718126615</v>
+        <v>1.356284453416969</v>
       </c>
       <c r="C17" t="n">
-        <v>11.35528664640031</v>
+        <v>9.930034416760002</v>
       </c>
       <c r="D17" t="n">
-        <v>5.59636443076556</v>
+        <v>6.912731022527855</v>
       </c>
       <c r="E17" t="n">
-        <v>18.35616879529248</v>
+        <v>18.19904989270482</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.592149339362265</v>
+        <v>1.538810986590536</v>
       </c>
       <c r="C18" t="n">
-        <v>13.37168843867579</v>
+        <v>11.59176021592224</v>
       </c>
       <c r="D18" t="n">
-        <v>6.009552587051916</v>
+        <v>7.398156174892689</v>
       </c>
       <c r="E18" t="n">
-        <v>20.97339036508997</v>
+        <v>20.52872737740546</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.584167730526739</v>
+        <v>1.536199537697239</v>
       </c>
       <c r="C19" t="n">
-        <v>14.40124725611942</v>
+        <v>12.40066141935936</v>
       </c>
       <c r="D19" t="n">
-        <v>6.077371718461285</v>
+        <v>7.531222258726302</v>
       </c>
       <c r="E19" t="n">
-        <v>22.06278670510744</v>
+        <v>21.4680832157829</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.752400017126472</v>
+        <v>1.704706713654162</v>
       </c>
       <c r="C20" t="n">
-        <v>16.62012469491876</v>
+        <v>14.30630243564171</v>
       </c>
       <c r="D20" t="n">
-        <v>6.445782361956943</v>
+        <v>8.041907779521408</v>
       </c>
       <c r="E20" t="n">
-        <v>24.81830707400218</v>
+        <v>24.05291692881728</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.036951377656609</v>
+        <v>1.011789183996763</v>
       </c>
       <c r="C21" t="n">
-        <v>12.29936469123517</v>
+        <v>10.54314567553918</v>
       </c>
       <c r="D21" t="n">
-        <v>5.359782868996165</v>
+        <v>6.736576031954848</v>
       </c>
       <c r="E21" t="n">
-        <v>18.69609893788794</v>
+        <v>18.29151089149079</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_30_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249368628705572</v>
+        <v>1.269013400267551</v>
       </c>
       <c r="C3" t="n">
-        <v>4.609459496888503</v>
+        <v>4.595479409580029</v>
       </c>
       <c r="D3" t="n">
-        <v>6.074941986827914</v>
+        <v>6.035976420446358</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93377011242199</v>
+        <v>11.90046923029394</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.362429431609629</v>
+        <v>1.416794534139102</v>
       </c>
       <c r="C4" t="n">
-        <v>5.093011461238112</v>
+        <v>5.041794240543146</v>
       </c>
       <c r="D4" t="n">
-        <v>6.459130576044458</v>
+        <v>6.252031572203632</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9145714688922</v>
+        <v>12.71062034688588</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.516044315992087</v>
+        <v>1.626811291420823</v>
       </c>
       <c r="C5" t="n">
-        <v>5.688695029372046</v>
+        <v>5.631545912180566</v>
       </c>
       <c r="D5" t="n">
-        <v>6.793234254444998</v>
+        <v>6.488823498805576</v>
       </c>
       <c r="E5" t="n">
-        <v>13.99797359980913</v>
+        <v>13.74718070240696</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.684064967212631</v>
+        <v>1.871049094373951</v>
       </c>
       <c r="C6" t="n">
-        <v>6.409086976530148</v>
+        <v>6.401736488629219</v>
       </c>
       <c r="D6" t="n">
-        <v>7.27789831219461</v>
+        <v>6.780064006671236</v>
       </c>
       <c r="E6" t="n">
-        <v>15.37105025593739</v>
+        <v>15.05284958967441</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.876735575466098</v>
+        <v>2.146268152465345</v>
       </c>
       <c r="C7" t="n">
-        <v>7.279311916748161</v>
+        <v>7.31422553476499</v>
       </c>
       <c r="D7" t="n">
-        <v>7.695149688141329</v>
+        <v>7.138642216558318</v>
       </c>
       <c r="E7" t="n">
-        <v>16.85119718035559</v>
+        <v>16.59913590378865</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.10873882453369</v>
+        <v>1.360553969862019</v>
       </c>
       <c r="C8" t="n">
-        <v>4.96606117075776</v>
+        <v>5.056896157236775</v>
       </c>
       <c r="D8" t="n">
-        <v>5.945571175853806</v>
+        <v>5.443854019098023</v>
       </c>
       <c r="E8" t="n">
-        <v>12.02037117114526</v>
+        <v>11.86130414619682</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.369934660081059</v>
+        <v>1.709681888367466</v>
       </c>
       <c r="C9" t="n">
-        <v>6.10816679582269</v>
+        <v>6.256229794505352</v>
       </c>
       <c r="D9" t="n">
-        <v>6.613852403009761</v>
+        <v>5.927356214504288</v>
       </c>
       <c r="E9" t="n">
-        <v>14.09195385891351</v>
+        <v>13.8932678973771</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.656393474781513</v>
+        <v>2.07965766511064</v>
       </c>
       <c r="C10" t="n">
-        <v>7.434116003821517</v>
+        <v>7.649524473483805</v>
       </c>
       <c r="D10" t="n">
-        <v>7.171321933479799</v>
+        <v>6.421967030902452</v>
       </c>
       <c r="E10" t="n">
-        <v>16.26183141208283</v>
+        <v>16.1511491694969</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.941532249639653</v>
+        <v>2.450514306760589</v>
       </c>
       <c r="C11" t="n">
-        <v>8.846662815665066</v>
+        <v>9.154521332577247</v>
       </c>
       <c r="D11" t="n">
-        <v>7.733531816960991</v>
+        <v>6.897781506756455</v>
       </c>
       <c r="E11" t="n">
-        <v>18.52172688226571</v>
+        <v>18.50281714609429</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.231235535447297</v>
+        <v>2.850441980414401</v>
       </c>
       <c r="C12" t="n">
-        <v>10.39789816479631</v>
+        <v>10.70889676578092</v>
       </c>
       <c r="D12" t="n">
-        <v>8.391370513008722</v>
+        <v>7.436515953300447</v>
       </c>
       <c r="E12" t="n">
-        <v>21.02050421325233</v>
+        <v>20.99585469949577</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.509484319887061</v>
+        <v>3.237874610989692</v>
       </c>
       <c r="C13" t="n">
-        <v>11.9484673495148</v>
+        <v>12.27277400721447</v>
       </c>
       <c r="D13" t="n">
-        <v>8.937738707451915</v>
+        <v>7.925032183207264</v>
       </c>
       <c r="E13" t="n">
-        <v>23.39569037685377</v>
+        <v>23.43568080141143</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.448038593855876</v>
+        <v>1.881342760602248</v>
       </c>
       <c r="C14" t="n">
-        <v>8.360357282347945</v>
+        <v>8.528766283534443</v>
       </c>
       <c r="D14" t="n">
-        <v>6.759656920481691</v>
+        <v>6.061889557165313</v>
       </c>
       <c r="E14" t="n">
-        <v>16.56805279668551</v>
+        <v>16.471998601302</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.471178387244973</v>
+        <v>1.944793114727719</v>
       </c>
       <c r="C15" t="n">
-        <v>9.049819060086396</v>
+        <v>9.174658098158421</v>
       </c>
       <c r="D15" t="n">
-        <v>6.834475913022341</v>
+        <v>6.093796357553335</v>
       </c>
       <c r="E15" t="n">
-        <v>17.35547336035371</v>
+        <v>17.21324757043947</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.696460032938488</v>
+        <v>2.276682743625396</v>
       </c>
       <c r="C16" t="n">
-        <v>10.7194675632219</v>
+        <v>10.75618492736073</v>
       </c>
       <c r="D16" t="n">
-        <v>7.394297906415</v>
+        <v>6.546058072468712</v>
       </c>
       <c r="E16" t="n">
-        <v>19.81022550257539</v>
+        <v>19.57892574345484</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.356284453416969</v>
+        <v>1.834739197081652</v>
       </c>
       <c r="C17" t="n">
-        <v>9.930034416760002</v>
+        <v>9.847626514465524</v>
       </c>
       <c r="D17" t="n">
-        <v>6.912731022527855</v>
+        <v>6.075545667731387</v>
       </c>
       <c r="E17" t="n">
-        <v>18.19904989270482</v>
+        <v>17.75791137927856</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.538810986590536</v>
+        <v>2.104484196300505</v>
       </c>
       <c r="C18" t="n">
-        <v>11.59176021592224</v>
+        <v>11.43474930558205</v>
       </c>
       <c r="D18" t="n">
-        <v>7.398156174892689</v>
+        <v>6.511883434883881</v>
       </c>
       <c r="E18" t="n">
-        <v>20.52872737740546</v>
+        <v>20.05111693676643</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.536199537697239</v>
+        <v>2.124835826209542</v>
       </c>
       <c r="C19" t="n">
-        <v>12.40066141935936</v>
+        <v>12.16605317047549</v>
       </c>
       <c r="D19" t="n">
-        <v>7.531222258726302</v>
+        <v>6.628780134028548</v>
       </c>
       <c r="E19" t="n">
-        <v>21.4680832157829</v>
+        <v>20.91966913071358</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.704706713654162</v>
+        <v>2.38393868031436</v>
       </c>
       <c r="C20" t="n">
-        <v>14.30630243564171</v>
+        <v>13.91650932714755</v>
       </c>
       <c r="D20" t="n">
-        <v>8.041907779521408</v>
+        <v>7.139927076244651</v>
       </c>
       <c r="E20" t="n">
-        <v>24.05291692881728</v>
+        <v>23.44037508370657</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.011789183996763</v>
+        <v>1.427844043579519</v>
       </c>
       <c r="C21" t="n">
-        <v>10.54314567553918</v>
+        <v>10.14396705899242</v>
       </c>
       <c r="D21" t="n">
-        <v>6.736576031954848</v>
+        <v>5.98518560903251</v>
       </c>
       <c r="E21" t="n">
-        <v>18.29151089149079</v>
+        <v>17.55699671160445</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_30_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_30_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.269013400267551</v>
+        <v>2.641205188095766</v>
       </c>
       <c r="C3" t="n">
-        <v>4.595479409580029</v>
+        <v>7.728020572876124</v>
       </c>
       <c r="D3" t="n">
-        <v>6.035976420446358</v>
+        <v>8.167667465492846</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90046923029394</v>
+        <v>18.53689322646473</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.416794534139102</v>
+        <v>1.192220476304173</v>
       </c>
       <c r="C4" t="n">
-        <v>5.041794240543146</v>
+        <v>4.519631130705586</v>
       </c>
       <c r="D4" t="n">
-        <v>6.252031572203632</v>
+        <v>5.69655150943354</v>
       </c>
       <c r="E4" t="n">
-        <v>12.71062034688588</v>
+        <v>11.4084031164433</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.626811291420823</v>
+        <v>1.394630877920444</v>
       </c>
       <c r="C5" t="n">
-        <v>5.631545912180566</v>
+        <v>5.146521277195528</v>
       </c>
       <c r="D5" t="n">
-        <v>6.488823498805576</v>
+        <v>5.910661642910677</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74718070240696</v>
+        <v>12.45181379802665</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.871049094373951</v>
+        <v>1.620996241206045</v>
       </c>
       <c r="C6" t="n">
-        <v>6.401736488629219</v>
+        <v>5.916293131290911</v>
       </c>
       <c r="D6" t="n">
-        <v>6.780064006671236</v>
+        <v>6.193364099187374</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05284958967441</v>
+        <v>13.73065347168433</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.146268152465345</v>
+        <v>1.851179202367342</v>
       </c>
       <c r="C7" t="n">
-        <v>7.31422553476499</v>
+        <v>6.814277137363702</v>
       </c>
       <c r="D7" t="n">
-        <v>7.138642216558318</v>
+        <v>6.610363715247741</v>
       </c>
       <c r="E7" t="n">
-        <v>16.59913590378865</v>
+        <v>15.27582005497879</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.360553969862019</v>
+        <v>2.082829078147711</v>
       </c>
       <c r="C8" t="n">
-        <v>5.056896157236775</v>
+        <v>7.84166428093681</v>
       </c>
       <c r="D8" t="n">
-        <v>5.443854019098023</v>
+        <v>7.020196139654693</v>
       </c>
       <c r="E8" t="n">
-        <v>11.86130414619682</v>
+        <v>16.94468949873922</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.709681888367466</v>
+        <v>2.289867559387955</v>
       </c>
       <c r="C9" t="n">
-        <v>6.256229794505352</v>
+        <v>8.950259620084026</v>
       </c>
       <c r="D9" t="n">
-        <v>5.927356214504288</v>
+        <v>7.387855661208089</v>
       </c>
       <c r="E9" t="n">
-        <v>13.8932678973771</v>
+        <v>18.62798284068007</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.07965766511064</v>
+        <v>1.362361471706256</v>
       </c>
       <c r="C10" t="n">
-        <v>7.649524473483805</v>
+        <v>6.627945648479938</v>
       </c>
       <c r="D10" t="n">
-        <v>6.421967030902452</v>
+        <v>5.84190934907473</v>
       </c>
       <c r="E10" t="n">
-        <v>16.1511491694969</v>
+        <v>13.83221646926092</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.450514306760589</v>
+        <v>1.3219625536765</v>
       </c>
       <c r="C11" t="n">
-        <v>9.154521332577247</v>
+        <v>6.929990147168514</v>
       </c>
       <c r="D11" t="n">
-        <v>6.897781506756455</v>
+        <v>5.687401895380368</v>
       </c>
       <c r="E11" t="n">
-        <v>18.50281714609429</v>
+        <v>13.93935459622538</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.850441980414401</v>
+        <v>1.471384554262865</v>
       </c>
       <c r="C12" t="n">
-        <v>10.70889676578092</v>
+        <v>8.08893349455483</v>
       </c>
       <c r="D12" t="n">
-        <v>7.436515953300447</v>
+        <v>6.08598164582753</v>
       </c>
       <c r="E12" t="n">
-        <v>20.99585469949577</v>
+        <v>15.64629969464522</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.237874610989692</v>
+        <v>1.176516631292335</v>
       </c>
       <c r="C13" t="n">
-        <v>12.27277400721447</v>
+        <v>7.598246174495232</v>
       </c>
       <c r="D13" t="n">
-        <v>7.925032183207264</v>
+        <v>5.562690484509894</v>
       </c>
       <c r="E13" t="n">
-        <v>23.43568080141143</v>
+        <v>14.33745329029746</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.881342760602248</v>
+        <v>1.31352934089702</v>
       </c>
       <c r="C14" t="n">
-        <v>8.528766283534443</v>
+        <v>8.848305526312695</v>
       </c>
       <c r="D14" t="n">
-        <v>6.061889557165313</v>
+        <v>5.930443357043708</v>
       </c>
       <c r="E14" t="n">
-        <v>16.471998601302</v>
+        <v>16.09227822425342</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.944793114727719</v>
+        <v>1.307776299350134</v>
       </c>
       <c r="C15" t="n">
-        <v>9.174658098158421</v>
+        <v>9.52258948454349</v>
       </c>
       <c r="D15" t="n">
-        <v>6.093796357553335</v>
+        <v>5.999715475055362</v>
       </c>
       <c r="E15" t="n">
-        <v>17.21324757043947</v>
+        <v>16.83008125894899</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.276682743625396</v>
+        <v>1.459318874977672</v>
       </c>
       <c r="C16" t="n">
-        <v>10.75618492736073</v>
+        <v>11.13949850100686</v>
       </c>
       <c r="D16" t="n">
-        <v>6.546058072468712</v>
+        <v>6.432784022352715</v>
       </c>
       <c r="E16" t="n">
-        <v>19.57892574345484</v>
+        <v>19.03160139833724</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.834739197081652</v>
+        <v>0.8836809260695967</v>
       </c>
       <c r="C17" t="n">
-        <v>9.847626514465524</v>
+        <v>8.415236979015344</v>
       </c>
       <c r="D17" t="n">
-        <v>6.075545667731387</v>
+        <v>5.367685938015351</v>
       </c>
       <c r="E17" t="n">
-        <v>17.75791137927856</v>
+        <v>14.66660384310029</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.104484196300505</v>
+        <v>0.7191989157000859</v>
       </c>
       <c r="C18" t="n">
-        <v>11.43474930558205</v>
+        <v>7.456177464213675</v>
       </c>
       <c r="D18" t="n">
-        <v>6.511883434883881</v>
+        <v>4.901002349324587</v>
       </c>
       <c r="E18" t="n">
-        <v>20.05111693676643</v>
+        <v>13.07637872923835</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.124835826209542</v>
+        <v>0.8576646119070561</v>
       </c>
       <c r="C19" t="n">
-        <v>12.16605317047549</v>
+        <v>9.284839643006039</v>
       </c>
       <c r="D19" t="n">
-        <v>6.628780134028548</v>
+        <v>5.389294204985823</v>
       </c>
       <c r="E19" t="n">
-        <v>20.91966913071358</v>
+        <v>15.53179845989892</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.38393868031436</v>
+        <v>0.9900925597329083</v>
       </c>
       <c r="C20" t="n">
-        <v>13.91650932714755</v>
+        <v>11.26084251725177</v>
       </c>
       <c r="D20" t="n">
-        <v>7.139927076244651</v>
+        <v>5.951276043327825</v>
       </c>
       <c r="E20" t="n">
-        <v>23.44037508370657</v>
+        <v>18.2022111203125</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.427844043579519</v>
+        <v>1.108550237727329</v>
       </c>
       <c r="C21" t="n">
-        <v>10.14396705899242</v>
+        <v>13.29808681328841</v>
       </c>
       <c r="D21" t="n">
-        <v>5.98518560903251</v>
+        <v>6.466860485167123</v>
       </c>
       <c r="E21" t="n">
-        <v>17.55699671160445</v>
+        <v>20.87349753618286</v>
       </c>
     </row>
   </sheetData>
